--- a/data/raw/inventory/Week 28/Tonor/Vendor SOH (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Tonor/Vendor SOH (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,87 +417,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>category_l0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>category_l1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>category_l2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>NLC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>OpenPOUnits</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Aged90PlusUnits</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>UnsellableUnits</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>SellableCost</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -518,12 +506,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA79114</t>
+          <t>FBA79582</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0CCVBQRFX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -533,25 +521,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TC310+</t>
+          <t>TD510+</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - USB - RGB</t>
+          <t>Hand held Mic + Boom Arm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>1689</v>
+        <v>3491</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -563,32 +551,32 @@
         <v>28</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>73164.78</v>
+        <v>4334.39</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79585</t>
+          <t>FBA79696</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -598,25 +586,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T20LP</t>
+          <t>TD310+</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Low Profile Boom Arm</t>
+          <t>Hand held Mic + Boom Arm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>845</v>
+        <v>927</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -628,32 +616,32 @@
         <v>28</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>13152.11</v>
+        <v>61357.94</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79578</t>
+          <t>FBA79585</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0CFKZ72N7</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -663,25 +651,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>T20LP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hand held Mic</t>
+          <t>Low Profile Boom Arm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1688</v>
+        <v>845</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -693,30 +681,32 @@
         <v>28</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>13152.11</v>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA79116</t>
+          <t>FBA77110</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -726,25 +716,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TC-777 PRO</t>
+          <t>TM20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tripod - RGB</t>
+          <t>Wired</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1086</v>
+        <v>1695</v>
       </c>
       <c r="I5" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -756,32 +746,32 @@
         <v>28</v>
       </c>
       <c r="M5" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>129379.6</v>
+        <v>110330.36</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA79577</t>
+          <t>FBA77114</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -791,25 +781,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TM310</t>
+          <t>TC-2030</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wired</t>
+          <t>Boom Arm Kit - USB</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>965</v>
+        <v>4423</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -821,32 +811,30 @@
         <v>28</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>6105.8</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA77116</t>
+          <t>FBA79116</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -856,7 +844,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TC40S</t>
+          <t>TC-777 PRO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -866,15 +854,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - USB - RGB</t>
+          <t>Tripod - RGB</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1930</v>
+        <v>1086</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -886,32 +874,32 @@
         <v>28</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
-        <v>10345.5</v>
+        <v>133824.54</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA79113</t>
+          <t>FBA79111</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -921,25 +909,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TC310</t>
+          <t>TD510</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tripod - RGB</t>
+          <t>USB/XLR Mic</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1206</v>
+        <v>2412</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -951,32 +939,32 @@
         <v>28</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>22765.06</v>
+        <v>12834.66</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA77113</t>
+          <t>FBA77111</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -986,25 +974,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>TC30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hand held Mic</t>
+          <t>Tripod</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>848</v>
+        <v>1327</v>
       </c>
       <c r="I9" t="n">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1016,32 +1004,32 @@
         <v>28</v>
       </c>
       <c r="M9" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>247338.73</v>
+        <v>98327.66</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA77111</t>
+          <t>FBK77102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1051,25 +1039,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TC30</t>
+          <t>G11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tripod</t>
+          <t>Wired</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1327</v>
+        <v>1108</v>
       </c>
       <c r="I10" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1081,32 +1069,32 @@
         <v>28</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>100078.82</v>
+        <v>90590.63</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBK77102</t>
+          <t>FBA77106</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1116,25 +1104,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>G11</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wired</t>
+          <t>Boom Arm Kit</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1108</v>
+        <v>1164</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1146,32 +1134,30 @@
         <v>28</v>
       </c>
       <c r="M11" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>92409.16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79575</t>
+          <t>FBA79697</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1181,25 +1167,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TC30+</t>
+          <t>TD310</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Boom Arm Kit</t>
+          <t>Hand held Mic + Stand</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1568</v>
+        <v>790</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1211,32 +1197,32 @@
         <v>28</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>22018.71</v>
+        <v>121231.66</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA77110</t>
+          <t>FBA79576</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1246,25 +1232,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TM20</t>
+          <t>TC30S+</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wired</t>
+          <t>Boom Arm Kit + RGB</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1695</v>
+        <v>1749</v>
       </c>
       <c r="I13" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1276,32 +1262,32 @@
         <v>28</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>4</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>110330.36</v>
+        <v>20413.89</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA79115</t>
+          <t>FBA77103</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0C8JDHLX9</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1311,22 +1297,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>ORCA001</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Boom Arm Kit</t>
+          <t>Stand</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>603</v>
+        <v>2412</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -1350,23 +1336,23 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2401.47</v>
+        <v>7528.69</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79574</t>
+          <t>FBA79577</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1376,25 +1362,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TC30S</t>
+          <t>TM310</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tripod+RGB</t>
+          <t>Wired</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1448</v>
+        <v>965</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1406,32 +1392,32 @@
         <v>28</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>13336.14</v>
+        <v>6105.8</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA77115</t>
+          <t>FBA77116</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1441,7 +1427,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TC40</t>
+          <t>TC40S</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1451,7 +1437,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - USB</t>
+          <t>Boom Arm Kit - USB - RGB</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1459,7 +1445,7 @@
         <v>1930</v>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1471,32 +1457,32 @@
         <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>22543.15</v>
+        <v>10345.5</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA77103</t>
+          <t>FBA79578</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0CFKZ72N7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1506,25 +1492,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ORCA001</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>Hand held Mic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>2412</v>
+        <v>1688</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1539,29 +1525,27 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="n">
-        <v>7528.69</v>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA79111</t>
+          <t>FBA79575</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1571,25 +1555,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TD510</t>
+          <t>TC30+</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USB/XLR Mic</t>
+          <t>Boom Arm Kit</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>2412</v>
+        <v>1568</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1601,32 +1585,32 @@
         <v>28</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>15840.56</v>
+        <v>19572.19</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA79696</t>
+          <t>FBA79114</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1636,25 +1620,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TD310+</t>
+          <t>TC310+</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hand held Mic + Boom Arm</t>
+          <t>Boom Arm Kit - USB - RGB</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>927</v>
+        <v>1689</v>
       </c>
       <c r="I19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1666,32 +1650,32 @@
         <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>61357.94</v>
+        <v>73164.78</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA77106</t>
+          <t>FBA77105</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1701,7 +1685,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T30</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1716,10 +1700,10 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1164</v>
+        <v>1477</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1731,7 +1715,7 @@
         <v>28</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1739,22 +1723,24 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>9531.450000000001</v>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA79579</t>
+          <t>FBA79115</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0CQX4GVSB</t>
+          <t>B0C8JDHLX9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1764,25 +1750,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hand held Mic</t>
+          <t>Boom Arm Kit</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1244</v>
+        <v>603</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1797,27 +1783,29 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>2401.47</v>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA77105</t>
+          <t>FBA79579</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0CQX4GVSB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1827,25 +1815,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Boom Arm Kit</t>
+          <t>Hand held Mic</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1477</v>
+        <v>1244</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1857,7 +1845,7 @@
         <v>28</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1865,24 +1853,22 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="P22" t="n">
-        <v>9531.450000000001</v>
-      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA77117</t>
+          <t>FBA77115</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1892,25 +1878,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>TC40</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Microphone Isolation Shield</t>
+          <t>Boom Arm Kit - USB</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1174</v>
+        <v>1930</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1922,32 +1908,32 @@
         <v>28</v>
       </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="n">
-        <v>8</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2</v>
-      </c>
       <c r="P23" t="n">
-        <v>62429.23</v>
+        <v>22543.15</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA77104</t>
+          <t>FBA77113</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B089SJGQBH</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1957,25 +1943,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TC20</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - XLR</t>
+          <t>Hand held Mic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>3015</v>
+        <v>848</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1987,30 +1973,32 @@
         <v>28</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>242321.76</v>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA77101</t>
+          <t>FBA77117</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2020,25 +2008,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TC-777</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tripod</t>
+          <t>Microphone Isolation Shield</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1206</v>
+        <v>1174</v>
       </c>
       <c r="I25" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2050,32 +2038,32 @@
         <v>28</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>70920.23</v>
+        <v>62429.23</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA79582</t>
+          <t>FBA79113</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0CCVBQRFX</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2085,25 +2073,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TD510+</t>
+          <t>TC310</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hand held Mic + Boom Arm</t>
+          <t>Tripod - RGB</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>3491</v>
+        <v>1206</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2115,32 +2103,32 @@
         <v>28</v>
       </c>
       <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>4334.39</v>
+        <v>22765.06</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA79697</t>
+          <t>FBA77101</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2150,25 +2138,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TD310</t>
+          <t>TC-777</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hand held Mic + Stand</t>
+          <t>Tripod</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>790</v>
+        <v>1206</v>
       </c>
       <c r="I27" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2180,32 +2168,32 @@
         <v>28</v>
       </c>
       <c r="M27" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P27" t="n">
-        <v>122915.43</v>
+        <v>70920.23</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA77114</t>
+          <t>FBA79574</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2215,7 +2203,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TC-2030</t>
+          <t>TC30S</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2225,15 +2213,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - USB</t>
+          <t>Tripod+RGB</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>4423</v>
+        <v>1448</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2245,7 +2233,7 @@
         <v>28</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2253,22 +2241,24 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>13336.14</v>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA79576</t>
+          <t>FBA77104</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B089SJGQBH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2278,7 +2268,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TC30S+</t>
+          <t>TC20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2288,15 +2278,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Boom Arm Kit + RGB</t>
+          <t>Boom Arm Kit - XLR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>1749</v>
+        <v>3015</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2311,17 +2301,15 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="P29" t="n">
-        <v>20413.89</v>
-      </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>

--- a/data/raw/inventory/Week 28/Tonor/Vendor SOH (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Tonor/Vendor SOH (SP-API).xlsx
@@ -506,12 +506,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA79582</t>
+          <t>FBA79578</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0CCVBQRFX</t>
+          <t>B0CFKZ72N7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TD510+</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -531,15 +531,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hand held Mic + Boom Arm</t>
+          <t>Hand held Mic</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>3491</v>
+        <v>1688</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         <v>28</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -559,9 +559,7 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>4334.39</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -571,12 +569,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79696</t>
+          <t>FBA77113</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -586,7 +584,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TD310+</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -596,15 +594,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hand held Mic + Boom Arm</t>
+          <t>Hand held Mic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>927</v>
+        <v>848</v>
       </c>
       <c r="I3" t="n">
-        <v>35</v>
+        <v>191</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -616,16 +614,16 @@
         <v>28</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>61357.94</v>
+        <v>242321.76</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -636,12 +634,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79585</t>
+          <t>FBA77115</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -651,22 +649,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T20LP</t>
+          <t>TC40</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Low Profile Boom Arm</t>
+          <t>Boom Arm Kit - USB</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>845</v>
+        <v>1930</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -681,16 +679,16 @@
         <v>28</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>13152.11</v>
+        <v>22543.15</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -701,12 +699,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA77110</t>
+          <t>FBA79116</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -716,25 +714,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TM20</t>
+          <t>TC-777 PRO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wired</t>
+          <t>Tripod - RGB</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1695</v>
+        <v>1086</v>
       </c>
       <c r="I5" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -746,16 +744,16 @@
         <v>28</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>110330.36</v>
+        <v>133824.54</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -766,12 +764,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA77114</t>
+          <t>FBA77103</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -781,7 +779,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TC-2030</t>
+          <t>ORCA001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -791,15 +789,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - USB</t>
+          <t>Stand</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>4423</v>
+        <v>2412</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -814,12 +812,14 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>7528.69</v>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -829,12 +829,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA79116</t>
+          <t>FBA77111</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TC-777 PRO</t>
+          <t>TC30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -854,15 +854,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tripod - RGB</t>
+          <t>Tripod</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1086</v>
+        <v>1327</v>
       </c>
       <c r="I7" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,16 +874,16 @@
         <v>28</v>
       </c>
       <c r="M7" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>133824.54</v>
+        <v>98327.66</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -894,12 +894,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA79111</t>
+          <t>FBA77106</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -909,25 +909,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TD510</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USB/XLR Mic</t>
+          <t>Boom Arm Kit</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>2412</v>
+        <v>1164</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,17 +939,15 @@
         <v>28</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
-        <v>12834.66</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -959,12 +957,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA77111</t>
+          <t>FBA79575</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -974,7 +972,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TC30</t>
+          <t>TC30+</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -984,15 +982,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tripod</t>
+          <t>Boom Arm Kit</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1327</v>
+        <v>1568</v>
       </c>
       <c r="I9" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,16 +1002,16 @@
         <v>28</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>98327.66</v>
+        <v>19572.19</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1024,12 +1022,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBK77102</t>
+          <t>FBA79574</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1039,25 +1037,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>G11</t>
+          <t>TC30S</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wired</t>
+          <t>Tripod+RGB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1108</v>
+        <v>1448</v>
       </c>
       <c r="I10" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,16 +1067,16 @@
         <v>28</v>
       </c>
       <c r="M10" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>90590.63</v>
+        <v>13336.14</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1089,12 +1087,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA77106</t>
+          <t>FBA79113</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1104,25 +1102,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>TC310</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Boom Arm Kit</t>
+          <t>Tripod - RGB</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1164</v>
+        <v>1206</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1137,12 +1135,14 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>22765.06</v>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -1152,12 +1152,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79697</t>
+          <t>FBA77101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1167,25 +1167,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TD310</t>
+          <t>TC-777</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hand held Mic + Stand</t>
+          <t>Tripod</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>790</v>
+        <v>1206</v>
       </c>
       <c r="I12" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1197,16 +1197,16 @@
         <v>28</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P12" t="n">
-        <v>121231.66</v>
+        <v>70920.23</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1217,12 +1217,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA79576</t>
+          <t>FBA79582</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0CCVBQRFX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1232,25 +1232,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TC30S+</t>
+          <t>TD510+</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Boom Arm Kit + RGB</t>
+          <t>Hand held Mic + Boom Arm</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1749</v>
+        <v>3491</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1262,16 +1262,16 @@
         <v>28</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>20413.89</v>
+        <v>4334.39</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1282,12 +1282,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA77103</t>
+          <t>FBA79577</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1297,25 +1297,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ORCA001</t>
+          <t>TM310</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>Wired</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>2412</v>
+        <v>965</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1327,16 +1327,16 @@
         <v>28</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>7528.69</v>
+        <v>6105.8</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1347,12 +1347,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79577</t>
+          <t>FBA77110</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TM310</t>
+          <t>TM20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1377,10 +1377,10 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>965</v>
+        <v>1695</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1392,16 +1392,16 @@
         <v>28</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
-        <v>6105.8</v>
+        <v>110330.36</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1477,12 +1477,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA79578</t>
+          <t>FBA79696</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0CFKZ72N7</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>TD310+</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1502,15 +1502,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hand held Mic</t>
+          <t>Hand held Mic + Boom Arm</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1688</v>
+        <v>927</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1522,15 +1522,17 @@
         <v>28</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>61357.94</v>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -1540,12 +1542,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA79575</t>
+          <t>FBA79579</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B0CQX4GVSB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1555,25 +1557,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TC30+</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Boom Arm Kit</t>
+          <t>Hand held Mic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1568</v>
+        <v>1244</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1588,14 +1590,12 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="P18" t="n">
-        <v>19572.19</v>
-      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -1605,12 +1605,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA79114</t>
+          <t>FBA77117</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1620,25 +1620,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TC310+</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - USB - RGB</t>
+          <t>Microphone Isolation Shield</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1689</v>
+        <v>1174</v>
       </c>
       <c r="I19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1650,16 +1650,16 @@
         <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>73164.78</v>
+        <v>62429.23</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1670,12 +1670,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA77105</t>
+          <t>FBA79576</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1685,25 +1685,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>TC30S+</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Boom Arm Kit</t>
+          <t>Boom Arm Kit + RGB</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1477</v>
+        <v>1749</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1715,16 +1715,16 @@
         <v>28</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>9531.450000000001</v>
+        <v>20413.89</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1735,12 +1735,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA79115</t>
+          <t>FBK77102</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0C8JDHLX9</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1750,25 +1750,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>G11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Boom Arm Kit</t>
+          <t>Wired</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>603</v>
+        <v>1108</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1780,16 +1780,16 @@
         <v>28</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>2401.47</v>
+        <v>90590.63</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1800,12 +1800,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA79579</t>
+          <t>FBA79115</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B0CQX4GVSB</t>
+          <t>B0C8JDHLX9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1815,25 +1815,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hand held Mic</t>
+          <t>Boom Arm Kit</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1244</v>
+        <v>603</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1848,12 +1848,14 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>2401.47</v>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -1863,12 +1865,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA77115</t>
+          <t>FBA79697</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1878,25 +1880,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TC40</t>
+          <t>TD310</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - USB</t>
+          <t>Hand held Mic + Stand</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1930</v>
+        <v>790</v>
       </c>
       <c r="I23" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1908,16 +1910,16 @@
         <v>28</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>22543.15</v>
+        <v>121231.66</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1928,12 +1930,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA77113</t>
+          <t>FBA77114</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1943,25 +1945,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>TC-2030</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hand held Mic</t>
+          <t>Boom Arm Kit - USB</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>848</v>
+        <v>4423</v>
       </c>
       <c r="I24" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1973,17 +1975,15 @@
         <v>28</v>
       </c>
       <c r="M24" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>242321.76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -1993,12 +1993,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA77117</t>
+          <t>FBA77104</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B089SJGQBH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2008,25 +2008,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>TC20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Microphone</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Microphone Isolation Shield</t>
+          <t>Boom Arm Kit - XLR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1174</v>
+        <v>3015</v>
       </c>
       <c r="I25" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2038,17 +2038,15 @@
         <v>28</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>62429.23</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>2026-07-11</t>
@@ -2058,12 +2056,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA79113</t>
+          <t>FBA77105</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2073,25 +2071,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TC310</t>
+          <t>T30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tripod - RGB</t>
+          <t>Boom Arm Kit</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>1206</v>
+        <v>1477</v>
       </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2103,16 +2101,16 @@
         <v>28</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>22765.06</v>
+        <v>9531.450000000001</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2123,12 +2121,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA77101</t>
+          <t>FBA79585</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2138,25 +2136,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TC-777</t>
+          <t>T20LP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tripod</t>
+          <t>Low Profile Boom Arm</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1206</v>
+        <v>845</v>
       </c>
       <c r="I27" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2168,16 +2166,16 @@
         <v>28</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>70920.23</v>
+        <v>13152.11</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2188,12 +2186,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA79574</t>
+          <t>FBA79111</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2203,25 +2201,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TC30S</t>
+          <t>TD510</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Condenser Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tripod+RGB</t>
+          <t>USB/XLR Mic</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>1448</v>
+        <v>2412</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2236,13 +2234,13 @@
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>13336.14</v>
+        <v>12834.66</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2253,12 +2251,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA77104</t>
+          <t>FBA79114</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B089SJGQBH</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2268,7 +2266,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TC20</t>
+          <t>TC310+</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2278,15 +2276,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Boom Arm Kit - XLR</t>
+          <t>Boom Arm Kit - USB - RGB</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>3015</v>
+        <v>1689</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2298,15 +2296,17 @@
         <v>28</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>73164.78</v>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>2026-07-11</t>
